--- a/mts/INS-PMSR.xlsx
+++ b/mts/INS-PMSR.xlsx
@@ -1926,7 +1926,7 @@
     <t>pmsr:/CSM1738147291317174</t>
   </si>
   <si>
-    <t xml:space="preserve">Tracheostomy care </t>
+    <t xml:space="preserve">Tracheostomy_care</t>
   </si>
   <si>
     <t>pmsr:/CSM1740441287738155</t>
